--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2020.xlsx
@@ -100,12 +100,6 @@
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
@@ -127,12 +121,6 @@
     <t xml:space="preserve">Natales</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">12302</t>
   </si>
   <si>
@@ -397,6 +385,12 @@
     <t xml:space="preserve">Chanco</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5302</t>
   </si>
   <si>
@@ -1099,6 +1093,12 @@
     <t xml:space="preserve">Alto Hospicio</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4204</t>
   </si>
   <si>
@@ -1834,7 +1834,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:22</t>
+    <t xml:space="preserve">2026-09-09 20:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2506,7 +2506,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>76.44</v>
+        <v>76.06</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2517,16 +2517,16 @@
         <v>2020</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2538,7 +2538,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>76.06</v>
+        <v>76.05</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2552,7 +2552,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -2570,7 +2570,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>76.05</v>
+        <v>74.22</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2584,7 +2584,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -2602,7 +2602,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>74.22</v>
+        <v>68.42</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2613,10 +2613,10 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -2634,7 +2634,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>73.22</v>
+        <v>68.15</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2648,7 +2648,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
@@ -2666,7 +2666,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>68.42</v>
+        <v>53.33</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2680,7 +2680,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>40</v>
@@ -2698,7 +2698,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>68.15</v>
+        <v>42.86</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2709,28 +2709,28 @@
         <v>2020</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>53.33</v>
+        <v>72.88</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -2741,28 +2741,28 @@
         <v>2020</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>42.86</v>
+        <v>72.56</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -2773,28 +2773,28 @@
         <v>2020</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>72.88</v>
+        <v>72.02</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -2808,7 +2808,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>52</v>
@@ -2817,16 +2817,16 @@
         <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>72.56</v>
+        <v>71.73</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -2840,7 +2840,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>54</v>
@@ -2849,16 +2849,16 @@
         <v>55</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>72.02</v>
+        <v>71.18</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -2869,10 +2869,10 @@
         <v>2020</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>56</v>
@@ -2881,16 +2881,16 @@
         <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>71.73</v>
+        <v>71.15</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -2904,7 +2904,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>58</v>
@@ -2913,16 +2913,16 @@
         <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>71.18</v>
+        <v>70.17</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -2933,28 +2933,28 @@
         <v>2020</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>71.15</v>
+        <v>69.84</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -2968,25 +2968,25 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>70.17</v>
+        <v>69.67</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -2997,10 +2997,10 @@
         <v>2020</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>65</v>
@@ -3009,16 +3009,16 @@
         <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>69.84</v>
+        <v>69.66</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3032,7 +3032,7 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
@@ -3041,16 +3041,16 @@
         <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>69.67</v>
+        <v>69.49</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3061,10 +3061,10 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>69</v>
@@ -3073,16 +3073,16 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>69.66</v>
+        <v>69.24</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3093,28 +3093,28 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>69.49</v>
+        <v>69.01</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3125,28 +3125,28 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>69.24</v>
+        <v>68.86</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3157,10 +3157,10 @@
         <v>2020</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3169,16 +3169,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>69.01</v>
+        <v>68.77</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3192,7 +3192,7 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3201,16 +3201,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>68.86</v>
+        <v>68.49</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3221,10 +3221,10 @@
         <v>2020</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3233,16 +3233,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>68.77</v>
+        <v>68.21</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3253,10 +3253,10 @@
         <v>2020</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3265,16 +3265,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>68.49</v>
+        <v>68.03</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3285,10 +3285,10 @@
         <v>2020</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3297,16 +3297,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>68.21</v>
+        <v>67.81</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3317,10 +3317,10 @@
         <v>2020</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3329,16 +3329,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>68.03</v>
+        <v>67.78</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3349,10 +3349,10 @@
         <v>2020</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3361,16 +3361,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>67.81</v>
+        <v>67.75</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3381,10 +3381,10 @@
         <v>2020</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3393,16 +3393,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>67.78</v>
+        <v>67.63</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3413,10 +3413,10 @@
         <v>2020</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3425,16 +3425,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>67.75</v>
+        <v>67.26</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3445,10 +3445,10 @@
         <v>2020</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3457,16 +3457,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>67.63</v>
+        <v>67.11</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3477,10 +3477,10 @@
         <v>2020</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3489,16 +3489,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>67.26</v>
+        <v>66.94</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3512,7 +3512,7 @@
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3521,16 +3521,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>67.11</v>
+        <v>66.92</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3541,10 +3541,10 @@
         <v>2020</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3553,16 +3553,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>66.94</v>
+        <v>66.85</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3573,10 +3573,10 @@
         <v>2020</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3585,16 +3585,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>66.92</v>
+        <v>66.67</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3605,10 +3605,10 @@
         <v>2020</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3617,16 +3617,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>66.85</v>
+        <v>66.6</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3637,10 +3637,10 @@
         <v>2020</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3649,16 +3649,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>66.67</v>
+        <v>66.57</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3669,10 +3669,10 @@
         <v>2020</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3681,16 +3681,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>66.6</v>
+        <v>66.4</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3701,10 +3701,10 @@
         <v>2020</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -3713,16 +3713,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>66.57</v>
+        <v>66.38</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -3733,10 +3733,10 @@
         <v>2020</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -3745,16 +3745,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>66.4</v>
+        <v>66.37</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -3765,10 +3765,10 @@
         <v>2020</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -3777,16 +3777,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>66.38</v>
+        <v>66.36</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -3797,10 +3797,10 @@
         <v>2020</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -3809,16 +3809,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>66.37</v>
+        <v>66.36</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -3829,10 +3829,10 @@
         <v>2020</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -3841,16 +3841,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>66.36</v>
+        <v>66.05</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -3861,10 +3861,10 @@
         <v>2020</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -3873,16 +3873,16 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>66.36</v>
+        <v>65.96</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -3896,7 +3896,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -3905,16 +3905,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>66.05</v>
+        <v>65.89</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -3925,10 +3925,10 @@
         <v>2020</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
@@ -3937,16 +3937,16 @@
         <v>125</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>65.96</v>
+        <v>65.85</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -3957,10 +3957,10 @@
         <v>2020</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -3969,16 +3969,16 @@
         <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>65.85</v>
+        <v>65.44</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -3992,7 +3992,7 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -4001,16 +4001,16 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>65.44</v>
+        <v>65.39</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4021,10 +4021,10 @@
         <v>2020</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -4033,16 +4033,16 @@
         <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>65.39</v>
+        <v>65.36</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4053,10 +4053,10 @@
         <v>2020</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4065,16 +4065,16 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>65.36</v>
+        <v>65.21</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4085,10 +4085,10 @@
         <v>2020</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4097,16 +4097,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>65.21</v>
+        <v>65.16</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4120,7 +4120,7 @@
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4129,16 +4129,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>65.16</v>
+        <v>65.15</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4149,10 +4149,10 @@
         <v>2020</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4161,16 +4161,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>65.15</v>
+        <v>65.06</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4181,10 +4181,10 @@
         <v>2020</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4193,16 +4193,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>65.06</v>
+        <v>65.03</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4213,10 +4213,10 @@
         <v>2020</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4225,16 +4225,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>65.03</v>
+        <v>64.99</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4245,10 +4245,10 @@
         <v>2020</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4257,16 +4257,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>64.99</v>
+        <v>64.82</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4280,7 +4280,7 @@
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4289,16 +4289,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>64.82</v>
+        <v>64.48</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4309,10 +4309,10 @@
         <v>2020</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4321,16 +4321,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>64.48</v>
+        <v>64.25</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4341,10 +4341,10 @@
         <v>2020</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4353,16 +4353,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>64.25</v>
+        <v>64.2</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4373,10 +4373,10 @@
         <v>2020</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4385,16 +4385,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>64.2</v>
+        <v>64.17</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4408,7 +4408,7 @@
         <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4417,16 +4417,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>64.17</v>
+        <v>63.86</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4440,7 +4440,7 @@
         <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4449,16 +4449,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>63.86</v>
+        <v>63.76</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4469,10 +4469,10 @@
         <v>2020</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4481,16 +4481,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>63.76</v>
+        <v>63.41</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4504,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4513,16 +4513,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>63.41</v>
+        <v>63.29</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4533,10 +4533,10 @@
         <v>2020</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4545,16 +4545,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>63.29</v>
+        <v>63.27</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4568,7 +4568,7 @@
         <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4577,16 +4577,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>63.27</v>
+        <v>63.18</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4600,7 +4600,7 @@
         <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4609,16 +4609,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>63.18</v>
+        <v>63.15</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4629,10 +4629,10 @@
         <v>2020</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4641,16 +4641,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>63.15</v>
+        <v>63.14</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4664,7 +4664,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4673,16 +4673,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>63.14</v>
+        <v>63.05</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4693,10 +4693,10 @@
         <v>2020</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4705,16 +4705,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>63.05</v>
+        <v>63.04</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -4725,10 +4725,10 @@
         <v>2020</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -4737,16 +4737,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>63.04</v>
+        <v>63.02</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -4757,10 +4757,10 @@
         <v>2020</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -4769,10 +4769,10 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -4789,10 +4789,10 @@
         <v>2020</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -4801,16 +4801,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>63.02</v>
+        <v>63</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -4821,10 +4821,10 @@
         <v>2020</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -4833,16 +4833,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>63</v>
+        <v>62.88</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -4853,10 +4853,10 @@
         <v>2020</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -4865,16 +4865,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>62.88</v>
+        <v>62.86</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -4888,7 +4888,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -4897,16 +4897,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>62.86</v>
+        <v>62.84</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -4920,7 +4920,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -4929,16 +4929,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>62.84</v>
+        <v>62.74</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -4949,10 +4949,10 @@
         <v>2020</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -4961,16 +4961,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>62.74</v>
+        <v>62.46</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -4984,7 +4984,7 @@
         <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -4993,16 +4993,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>62.46</v>
+        <v>62.3</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5016,7 +5016,7 @@
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5025,16 +5025,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>62.3</v>
+        <v>62.22</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5045,28 +5045,28 @@
         <v>2020</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>62.22</v>
+        <v>62.06</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5077,10 +5077,10 @@
         <v>2020</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>197</v>
@@ -5089,16 +5089,16 @@
         <v>198</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>62.06</v>
+        <v>62.05</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5109,10 +5109,10 @@
         <v>2020</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>199</v>
@@ -5121,16 +5121,16 @@
         <v>200</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>62.05</v>
+        <v>62.04</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5141,10 +5141,10 @@
         <v>2020</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>201</v>
@@ -5153,16 +5153,16 @@
         <v>202</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>62.04</v>
+        <v>61.99</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5173,10 +5173,10 @@
         <v>2020</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>196</v>
+        <v>42</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>203</v>
@@ -5185,16 +5185,16 @@
         <v>204</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>61.99</v>
+        <v>61.95</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5205,10 +5205,10 @@
         <v>2020</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>205</v>
@@ -5217,16 +5217,16 @@
         <v>206</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>61.95</v>
+        <v>61.94</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5240,7 +5240,7 @@
         <v>6</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>207</v>
@@ -5249,16 +5249,16 @@
         <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>61.94</v>
+        <v>61.92</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5272,7 +5272,7 @@
         <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>209</v>
@@ -5281,16 +5281,16 @@
         <v>210</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>61.92</v>
+        <v>61.63</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5301,10 +5301,10 @@
         <v>2020</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>211</v>
@@ -5313,16 +5313,16 @@
         <v>212</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>61.63</v>
+        <v>61.59</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5336,7 +5336,7 @@
         <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>213</v>
@@ -5345,16 +5345,16 @@
         <v>214</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>61.59</v>
+        <v>61.57</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5365,10 +5365,10 @@
         <v>2020</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>196</v>
+        <v>42</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>215</v>
@@ -5377,16 +5377,16 @@
         <v>216</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>61.57</v>
+        <v>61.55</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5397,10 +5397,10 @@
         <v>2020</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>217</v>
@@ -5409,16 +5409,16 @@
         <v>218</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>61.55</v>
+        <v>61.52</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5429,10 +5429,10 @@
         <v>2020</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>219</v>
@@ -5441,16 +5441,16 @@
         <v>220</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>61.52</v>
+        <v>61.47</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5464,7 +5464,7 @@
         <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>221</v>
@@ -5473,16 +5473,16 @@
         <v>222</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>61.47</v>
+        <v>61.3</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5493,10 +5493,10 @@
         <v>2020</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>223</v>
@@ -5505,10 +5505,10 @@
         <v>224</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5525,10 +5525,10 @@
         <v>2020</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>225</v>
@@ -5537,16 +5537,16 @@
         <v>226</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>61.3</v>
+        <v>61.19</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5557,10 +5557,10 @@
         <v>2020</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>227</v>
@@ -5569,16 +5569,16 @@
         <v>228</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>61.19</v>
+        <v>61.03</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5589,10 +5589,10 @@
         <v>2020</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>196</v>
+        <v>60</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>229</v>
@@ -5601,16 +5601,16 @@
         <v>230</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>61.03</v>
+        <v>60.95</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5621,10 +5621,10 @@
         <v>2020</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>231</v>
@@ -5633,16 +5633,16 @@
         <v>232</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>60.95</v>
+        <v>60.83</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5656,7 +5656,7 @@
         <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>233</v>
@@ -5665,16 +5665,16 @@
         <v>234</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>60.83</v>
+        <v>60.82</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -5685,10 +5685,10 @@
         <v>2020</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>235</v>
@@ -5697,16 +5697,16 @@
         <v>236</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>60.82</v>
+        <v>60.74</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5717,10 +5717,10 @@
         <v>2020</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>237</v>
@@ -5729,16 +5729,16 @@
         <v>238</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>60.74</v>
+        <v>60.73</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -5752,7 +5752,7 @@
         <v>6</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>239</v>
@@ -5761,16 +5761,16 @@
         <v>240</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>60.73</v>
+        <v>60.67</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -5781,10 +5781,10 @@
         <v>2020</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>241</v>
@@ -5793,16 +5793,16 @@
         <v>242</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>60.67</v>
+        <v>60.64</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -5816,7 +5816,7 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>243</v>
@@ -5825,16 +5825,16 @@
         <v>244</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>60.64</v>
+        <v>60.62</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -5845,10 +5845,10 @@
         <v>2020</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>196</v>
+        <v>42</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>245</v>
@@ -5857,16 +5857,16 @@
         <v>246</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>60.62</v>
+        <v>60.51</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -5877,10 +5877,10 @@
         <v>2020</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>247</v>
@@ -5889,16 +5889,16 @@
         <v>248</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>60.51</v>
+        <v>60.45</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -5909,10 +5909,10 @@
         <v>2020</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>249</v>
@@ -5921,16 +5921,16 @@
         <v>250</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>60.45</v>
+        <v>60.43</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -5941,10 +5941,10 @@
         <v>2020</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>251</v>
@@ -5953,16 +5953,16 @@
         <v>252</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>60.43</v>
+        <v>60.42</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -5973,10 +5973,10 @@
         <v>2020</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>253</v>
@@ -5985,16 +5985,16 @@
         <v>254</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>60.42</v>
+        <v>60.36</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6005,10 +6005,10 @@
         <v>2020</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>255</v>
@@ -6017,16 +6017,16 @@
         <v>256</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>60.36</v>
+        <v>60.16</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6037,10 +6037,10 @@
         <v>2020</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>257</v>
@@ -6049,16 +6049,16 @@
         <v>258</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>60.16</v>
+        <v>60.1</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6069,10 +6069,10 @@
         <v>2020</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>196</v>
+        <v>60</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>259</v>
@@ -6081,10 +6081,10 @@
         <v>260</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6101,10 +6101,10 @@
         <v>2020</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>261</v>
@@ -6113,16 +6113,16 @@
         <v>262</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>60.1</v>
+        <v>59.78</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6133,10 +6133,10 @@
         <v>2020</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>263</v>
@@ -6145,16 +6145,16 @@
         <v>264</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>59.78</v>
+        <v>59.27</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6168,7 +6168,7 @@
         <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>265</v>
@@ -6177,16 +6177,16 @@
         <v>266</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>59.27</v>
+        <v>59.21</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6197,10 +6197,10 @@
         <v>2020</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>267</v>
@@ -6209,16 +6209,16 @@
         <v>268</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>59.21</v>
+        <v>58.74</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6232,7 +6232,7 @@
         <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>269</v>
@@ -6241,16 +6241,16 @@
         <v>270</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>58.74</v>
+        <v>58.59</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6261,10 +6261,10 @@
         <v>2020</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>271</v>
@@ -6273,16 +6273,16 @@
         <v>272</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>58.59</v>
+        <v>58.58</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6296,7 +6296,7 @@
         <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>273</v>
@@ -6305,16 +6305,16 @@
         <v>274</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>58.58</v>
+        <v>58.56</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6325,10 +6325,10 @@
         <v>2020</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>275</v>
@@ -6337,16 +6337,16 @@
         <v>276</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>58.56</v>
+        <v>58.37</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6357,10 +6357,10 @@
         <v>2020</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>277</v>
@@ -6369,16 +6369,16 @@
         <v>278</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>58.37</v>
+        <v>58.29</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6389,10 +6389,10 @@
         <v>2020</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>279</v>
@@ -6401,10 +6401,10 @@
         <v>280</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6421,10 +6421,10 @@
         <v>2020</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>281</v>
@@ -6433,16 +6433,16 @@
         <v>282</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>58.29</v>
+        <v>57.56</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6456,7 +6456,7 @@
         <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>283</v>
@@ -6465,16 +6465,16 @@
         <v>284</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>57.56</v>
+        <v>57.31</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6485,10 +6485,10 @@
         <v>2020</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>285</v>
@@ -6497,16 +6497,16 @@
         <v>286</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>57.31</v>
+        <v>57.21</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6520,7 +6520,7 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>287</v>
@@ -6529,16 +6529,16 @@
         <v>288</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>57.21</v>
+        <v>56.98</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6552,7 +6552,7 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>289</v>
@@ -6561,16 +6561,16 @@
         <v>290</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>56.98</v>
+        <v>56.65</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6581,10 +6581,10 @@
         <v>2020</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>291</v>
@@ -6593,16 +6593,16 @@
         <v>292</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>56.65</v>
+        <v>56.25</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6613,10 +6613,10 @@
         <v>2020</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>293</v>
@@ -6625,16 +6625,16 @@
         <v>294</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>56.25</v>
+        <v>55.71</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6645,10 +6645,10 @@
         <v>2020</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>295</v>
@@ -6657,16 +6657,16 @@
         <v>296</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>55.71</v>
+        <v>55.6</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6680,7 +6680,7 @@
         <v>13</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>297</v>
@@ -6689,16 +6689,16 @@
         <v>298</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>55.6</v>
+        <v>55.39</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6709,10 +6709,10 @@
         <v>2020</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>196</v>
+        <v>60</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>299</v>
@@ -6721,16 +6721,16 @@
         <v>300</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>55.39</v>
+        <v>55.19</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -6741,10 +6741,10 @@
         <v>2020</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>301</v>
@@ -6753,16 +6753,16 @@
         <v>302</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>55.19</v>
+        <v>54.14</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -6776,7 +6776,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>303</v>
@@ -6785,16 +6785,16 @@
         <v>304</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>54.14</v>
+        <v>54.11</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -6805,10 +6805,10 @@
         <v>2020</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>305</v>
@@ -6817,16 +6817,16 @@
         <v>306</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>54.11</v>
+        <v>53.86</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -6837,10 +6837,10 @@
         <v>2020</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>307</v>
@@ -6849,16 +6849,16 @@
         <v>308</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>53.86</v>
+        <v>53.3</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -6869,10 +6869,10 @@
         <v>2020</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>309</v>
@@ -6881,16 +6881,16 @@
         <v>310</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>53.3</v>
+        <v>53.29</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -6904,7 +6904,7 @@
         <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>311</v>
@@ -6913,16 +6913,16 @@
         <v>312</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>53.29</v>
+        <v>52.39</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -6933,10 +6933,10 @@
         <v>2020</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>313</v>
@@ -6945,16 +6945,16 @@
         <v>314</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>52.39</v>
+        <v>51.56</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -6968,7 +6968,7 @@
         <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>315</v>
@@ -6977,16 +6977,16 @@
         <v>316</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>51.56</v>
+        <v>51.08</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -6997,10 +6997,10 @@
         <v>2020</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>196</v>
+        <v>42</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>317</v>
@@ -7009,16 +7009,16 @@
         <v>318</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>51.08</v>
+        <v>50.18</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7029,10 +7029,10 @@
         <v>2020</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>319</v>
@@ -7041,16 +7041,16 @@
         <v>320</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>50.18</v>
+        <v>49.25</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7064,7 +7064,7 @@
         <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>321</v>
@@ -7073,16 +7073,16 @@
         <v>322</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>49.25</v>
+        <v>47.67</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7096,7 +7096,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>323</v>
@@ -7105,16 +7105,16 @@
         <v>324</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>47.67</v>
+        <v>41.27</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7128,7 +7128,7 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>325</v>
@@ -7137,16 +7137,16 @@
         <v>326</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>41.27</v>
+        <v>40.36</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7157,28 +7157,28 @@
         <v>2020</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>196</v>
+        <v>327</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>49</v>
+        <v>330</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>50</v>
+        <v>331</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>40.36</v>
+        <v>71.43</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7189,28 +7189,28 @@
         <v>2020</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D155" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E155" s="2" t="s">
+      <c r="G155" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="F155" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>333</v>
-      </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>71.43</v>
+        <v>70.31</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7221,10 +7221,10 @@
         <v>2020</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>335</v>
@@ -7233,16 +7233,16 @@
         <v>336</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>70.31</v>
+        <v>69.47</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7253,28 +7253,28 @@
         <v>2020</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>69.47</v>
+        <v>69.39</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7285,10 +7285,10 @@
         <v>2020</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>340</v>
@@ -7297,16 +7297,16 @@
         <v>341</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>69.39</v>
+        <v>69.01</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7320,7 +7320,7 @@
         <v>3</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>342</v>
@@ -7329,16 +7329,16 @@
         <v>343</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>69.01</v>
+        <v>68.32</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7349,28 +7349,28 @@
         <v>2020</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>68.32</v>
+        <v>67.4</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7381,10 +7381,10 @@
         <v>2020</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>347</v>
@@ -7393,16 +7393,16 @@
         <v>348</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>67.4</v>
+        <v>67.11</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7413,28 +7413,28 @@
         <v>2020</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>67.11</v>
+        <v>66.67</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7445,10 +7445,10 @@
         <v>2020</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>352</v>
@@ -7457,16 +7457,16 @@
         <v>353</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>66.67</v>
+        <v>66.03</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7477,10 +7477,10 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>354</v>
@@ -7489,16 +7489,16 @@
         <v>355</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>66.03</v>
+        <v>65.64</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7512,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>356</v>
@@ -7521,16 +7521,16 @@
         <v>357</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>65.64</v>
+        <v>65.58</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7541,10 +7541,10 @@
         <v>2020</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>358</v>
@@ -7553,16 +7553,16 @@
         <v>359</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>65.58</v>
+        <v>65.54</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7576,7 +7576,7 @@
         <v>4</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>360</v>
@@ -7585,10 +7585,10 @@
         <v>361</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7608,7 +7608,7 @@
         <v>4</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>362</v>
@@ -7617,10 +7617,10 @@
         <v>363</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7640,7 +7640,7 @@
         <v>15</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>364</v>
@@ -7649,10 +7649,10 @@
         <v>365</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7672,7 +7672,7 @@
         <v>4</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>366</v>
@@ -7681,10 +7681,10 @@
         <v>367</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7704,7 +7704,7 @@
         <v>3</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>368</v>
@@ -7713,10 +7713,10 @@
         <v>369</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -7736,7 +7736,7 @@
         <v>2</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>370</v>
@@ -7745,10 +7745,10 @@
         <v>371</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -7768,7 +7768,7 @@
         <v>4</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>372</v>
@@ -7777,10 +7777,10 @@
         <v>373</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -7800,7 +7800,7 @@
         <v>4</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>374</v>
@@ -7809,10 +7809,10 @@
         <v>375</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -7832,7 +7832,7 @@
         <v>3</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>376</v>
@@ -7841,10 +7841,10 @@
         <v>377</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -7864,7 +7864,7 @@
         <v>2</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>378</v>
@@ -7873,10 +7873,10 @@
         <v>379</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -7896,7 +7896,7 @@
         <v>4</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>380</v>
@@ -7905,10 +7905,10 @@
         <v>381</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -7928,7 +7928,7 @@
         <v>4</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>382</v>
@@ -7937,10 +7937,10 @@
         <v>383</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -7960,7 +7960,7 @@
         <v>2</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>384</v>
@@ -7969,10 +7969,10 @@
         <v>385</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -7992,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>386</v>
@@ -8001,10 +8001,10 @@
         <v>387</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8024,7 +8024,7 @@
         <v>4</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>388</v>
@@ -8033,10 +8033,10 @@
         <v>389</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8056,7 +8056,7 @@
         <v>15</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>390</v>
@@ -8065,10 +8065,10 @@
         <v>391</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8088,7 +8088,7 @@
         <v>4</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>392</v>
@@ -8097,10 +8097,10 @@
         <v>393</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8120,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>394</v>
@@ -8129,10 +8129,10 @@
         <v>395</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8152,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>396</v>
@@ -8161,10 +8161,10 @@
         <v>397</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8184,7 +8184,7 @@
         <v>1</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>398</v>
@@ -8193,10 +8193,10 @@
         <v>399</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2020.xlsx
@@ -1834,7 +1834,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:09</t>
+    <t xml:space="preserve">2026-09-18 11:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2020.xlsx
@@ -1834,7 +1834,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:30</t>
+    <t xml:space="preserve">2026-09-24 00:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
